--- a/docs/db_schema_cg-toolbox.xlsx
+++ b/docs/db_schema_cg-toolbox.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://compugraf-my.sharepoint.com/personal/rsilva_cg-one_com/Documents/Documents/Aplicacoes/CheckPointAssistant/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://compugraf-my.sharepoint.com/personal/rsilva_cg-one_com/Documents/Documents/Aplicacoes/cg-toolbox/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_9D3999AD126CC82CA16492DAB6B15E9E144FDCCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EF8C83C-9884-4296-A990-2F22105C5DED}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_9D3999AD126CC82CA16492DAB6B15E9E144FDCCB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25C8C68C-3A6B-4ECA-B97F-9AAA64C03B09}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Visão Geral" sheetId="1" r:id="rId1"/>
@@ -817,6 +817,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1105,7 +1109,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1113,7 +1117,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1127,7 +1131,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1141,7 +1145,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -1155,7 +1159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1169,7 +1173,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1183,7 +1187,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1197,7 +1201,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>15</v>
       </c>
@@ -1211,7 +1215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>18</v>
       </c>
@@ -1225,7 +1229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>20</v>
       </c>
@@ -1239,7 +1243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>22</v>
       </c>
@@ -1253,7 +1257,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>25</v>
       </c>
@@ -1267,7 +1271,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>27</v>
       </c>
@@ -1281,7 +1285,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>29</v>
       </c>
@@ -1295,7 +1299,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>31</v>
       </c>
@@ -1309,7 +1313,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>34</v>
       </c>
@@ -1331,16 +1335,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G85"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="62" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1363,7 +1369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>4</v>
       </c>
@@ -1386,7 +1392,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>4</v>
       </c>
@@ -1407,7 +1413,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>4</v>
       </c>
@@ -1428,7 +1434,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>4</v>
       </c>
@@ -1449,7 +1455,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>4</v>
       </c>
@@ -1470,7 +1476,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>4</v>
       </c>
@@ -1491,7 +1497,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>4</v>
       </c>
@@ -1512,7 +1518,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>4</v>
       </c>
@@ -1533,7 +1539,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>4</v>
       </c>
@@ -1554,7 +1560,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>4</v>
       </c>
@@ -1575,7 +1581,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>4</v>
       </c>
@@ -1596,7 +1602,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>4</v>
       </c>
@@ -1617,7 +1623,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>4</v>
       </c>
@@ -1638,7 +1644,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>4</v>
       </c>
@@ -1659,7 +1665,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>4</v>
       </c>
@@ -1680,7 +1686,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>4</v>
       </c>
@@ -1701,7 +1707,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>4</v>
       </c>
@@ -1722,7 +1728,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>4</v>
       </c>
@@ -1743,7 +1749,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>4</v>
       </c>
@@ -1764,7 +1770,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>4</v>
       </c>
@@ -1785,7 +1791,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>4</v>
       </c>
@@ -1806,7 +1812,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>4</v>
       </c>
@@ -1827,7 +1833,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>4</v>
       </c>
@@ -1848,7 +1854,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>4</v>
       </c>
@@ -1869,7 +1875,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>4</v>
       </c>
@@ -1890,7 +1896,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>15</v>
       </c>
@@ -1913,7 +1919,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>15</v>
       </c>
@@ -1936,7 +1942,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>18</v>
       </c>
@@ -1959,7 +1965,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>18</v>
       </c>
@@ -1982,7 +1988,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>20</v>
       </c>
@@ -2005,7 +2011,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>20</v>
       </c>
@@ -2028,7 +2034,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
         <v>22</v>
       </c>
@@ -2051,7 +2057,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>22</v>
       </c>
@@ -2072,7 +2078,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>22</v>
       </c>
@@ -2093,7 +2099,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>22</v>
       </c>
@@ -2114,7 +2120,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>25</v>
       </c>
@@ -2137,7 +2143,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>25</v>
       </c>
@@ -2158,7 +2164,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>25</v>
       </c>
@@ -2179,7 +2185,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>25</v>
       </c>
@@ -2200,7 +2206,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
         <v>27</v>
       </c>
@@ -2223,7 +2229,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>27</v>
       </c>
@@ -2244,7 +2250,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>27</v>
       </c>
@@ -2265,7 +2271,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>27</v>
       </c>
@@ -2286,7 +2292,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>27</v>
       </c>
@@ -2307,7 +2313,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>27</v>
       </c>
@@ -2328,7 +2334,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>29</v>
       </c>
@@ -2351,7 +2357,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>29</v>
       </c>
@@ -2372,7 +2378,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>29</v>
       </c>
@@ -2393,7 +2399,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>29</v>
       </c>
@@ -2414,7 +2420,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="11" t="s">
         <v>13</v>
       </c>
@@ -2437,7 +2443,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
         <v>13</v>
       </c>
@@ -2460,7 +2466,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
         <v>13</v>
       </c>
@@ -2481,7 +2487,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>13</v>
       </c>
@@ -2502,7 +2508,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>13</v>
       </c>
@@ -2523,7 +2529,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>13</v>
       </c>
@@ -2544,7 +2550,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>7</v>
       </c>
@@ -2567,7 +2573,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
         <v>7</v>
       </c>
@@ -2590,7 +2596,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
         <v>7</v>
       </c>
@@ -2611,7 +2617,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
         <v>7</v>
       </c>
@@ -2632,7 +2638,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
         <v>7</v>
       </c>
@@ -2653,7 +2659,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
         <v>7</v>
       </c>
@@ -2674,7 +2680,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
         <v>7</v>
       </c>
@@ -2695,7 +2701,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
         <v>7</v>
       </c>
@@ -2716,7 +2722,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
         <v>7</v>
       </c>
@@ -2737,7 +2743,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="11" t="s">
         <v>9</v>
       </c>
@@ -2760,7 +2766,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="11" t="s">
         <v>9</v>
       </c>
@@ -2783,7 +2789,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="11" t="s">
         <v>9</v>
       </c>
@@ -2804,7 +2810,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="11" t="s">
         <v>9</v>
       </c>
@@ -2825,7 +2831,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="11" t="s">
         <v>9</v>
       </c>
@@ -2846,7 +2852,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="11" t="s">
         <v>9</v>
       </c>
@@ -2867,7 +2873,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
         <v>11</v>
       </c>
@@ -2890,7 +2896,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
         <v>11</v>
       </c>
@@ -2913,7 +2919,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
         <v>11</v>
       </c>
@@ -2934,7 +2940,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
         <v>11</v>
       </c>
@@ -2955,7 +2961,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
         <v>11</v>
       </c>
@@ -2976,7 +2982,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
         <v>11</v>
       </c>
@@ -2997,7 +3003,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
         <v>11</v>
       </c>
@@ -3018,7 +3024,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>31</v>
       </c>
@@ -3041,7 +3047,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="11" t="s">
         <v>31</v>
       </c>
@@ -3064,7 +3070,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="11" t="s">
         <v>31</v>
       </c>
@@ -3085,7 +3091,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
         <v>34</v>
       </c>
@@ -3108,7 +3114,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
         <v>34</v>
       </c>
@@ -3131,7 +3137,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="14" t="s">
         <v>34</v>
       </c>
@@ -3152,7 +3158,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="14" t="s">
         <v>34</v>
       </c>
@@ -3182,7 +3188,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -3191,7 +3197,7 @@
     <col min="5" max="5" width="46" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>177</v>
       </c>
@@ -3208,7 +3214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
@@ -3225,7 +3231,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>18</v>
       </c>
@@ -3242,7 +3248,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
@@ -3259,7 +3265,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>13</v>
       </c>
@@ -3276,7 +3282,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>7</v>
       </c>
@@ -3293,7 +3299,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>9</v>
       </c>
@@ -3310,7 +3316,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
@@ -3327,7 +3333,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>31</v>
       </c>
@@ -3344,14 +3350,14 @@
         <v>190</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="4"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>191</v>
       </c>
@@ -3360,7 +3366,7 @@
       <c r="D11" s="18"/>
       <c r="E11" s="17"/>
     </row>
-    <row r="12" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
@@ -3377,7 +3383,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>18</v>
       </c>
@@ -3394,7 +3400,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>20</v>
       </c>
@@ -3411,7 +3417,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="26" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>4</v>
       </c>
@@ -3436,14 +3442,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>197</v>
       </c>
@@ -3454,7 +3460,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>199</v>
       </c>
@@ -3465,7 +3471,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>200</v>
       </c>
@@ -3476,7 +3482,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>201</v>
       </c>
@@ -3487,7 +3493,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>202</v>
       </c>
@@ -3498,7 +3504,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>203</v>
       </c>
